--- a/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:39</t>
+          <t>2026-09-09 00:51:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:40</t>
+          <t>2026-09-09 00:51:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:41</t>
+          <t>2026-09-09 00:51:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:43</t>
+          <t>2026-09-09 00:51:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:43</t>
+          <t>2026-09-09 00:51:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:43</t>
+          <t>2026-09-09 00:51:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:43</t>
+          <t>2026-09-09 00:51:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:43</t>
+          <t>2026-09-09 00:51:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:43</t>
+          <t>2026-09-09 00:51:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.17%341,000</t>
+          <t>8.33%341,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.17%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.16%133,000</t>
+          <t>6.18%133,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.18%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.30%99,000</t>
+          <t>5.21%99,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.28%80,000</t>
+          <t>4.57%80,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>+0.64%236.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12520</v>
+        <v>236.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.79%28,000</t>
+          <t>3.87%1,669,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>28000</v>
+        <v>1669000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.95%235</t>
+          <t>-1.51%523</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>235</v>
+        <v>523</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.74%1,669,000</t>
+          <t>3.58%684,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1669000</v>
+        <v>684000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3285</v>
+        <v>12400</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.50%105,000</t>
+          <t>3.46%28,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>105000</v>
+        <v>28000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.71%531</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>531</v>
+        <v>3380</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.44%684,000</t>
+          <t>3.40%105,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>684000</v>
+        <v>105000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.25%134,191</t>
+          <t>3.10%134,191</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.98%323,000</t>
+          <t>3.04%323,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19220</v>
+        <v>18605</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.92%15,600</t>
+          <t>2.96%15,600</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.89%50,000</t>
+          <t>2.94%50,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1955</v>
+        <v>2015</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.82%138,000</t>
+          <t>2.66%138,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.55%191,000</t>
+          <t>2.53%191,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:47</t>
+          <t>2026-09-09 19:34:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.44%188</t>
+          <t>-5.45%7280</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>188</v>
+        <v>7280</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.21%1,262,000</t>
+          <t>2.43%32,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1262000</v>
+        <v>32000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2368金像電子</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>-2.66%183</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1075</v>
+        <v>183</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.18%200,000</t>
+          <t>2.34%1,262,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>200000</v>
+        <v>1262000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+10%7700</t>
+          <t>+1.5%812</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7700</v>
+        <v>812</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.18%32,000</t>
+          <t>2.15%273,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>32000</v>
+        <v>273000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>2368金像電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.6%800</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.16%273,000</t>
+          <t>2.12%200,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>273000</v>
+        <v>200000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.05%114,000</t>
+          <t>2.03%114,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>-0.59%502</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1935</v>
+        <v>502</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.01%100,000</t>
+          <t>2.00%401,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>100000</v>
+        <v>401000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.8%505</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>505</v>
+        <v>1975</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.96%401,000</t>
+          <t>1.91%100,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>401000</v>
+        <v>100000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1025</v>
+        <v>1110</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.89%185,000</t>
+          <t>1.87%185,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.33%186.5</t>
+          <t>+1.34%189</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>186.5</v>
+        <v>189</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.83%953,000</t>
+          <t>1.75%953,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.73%1,241,000</t>
+          <t>1.68%1,241,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+3.5%533</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6500</v>
+        <v>533</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.62%25,000</t>
+          <t>1.66%327,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>25000</v>
+        <v>327000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3%515</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>515</v>
+        <v>6870</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.59%327,000</t>
+          <t>1.60%25,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>327000</v>
+        <v>25000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1225</v>
+        <v>1345</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.54%128,000</t>
+          <t>1.55%128,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.40%47,000</t>
+          <t>1.33%47,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.88%225</t>
+          <t>+3.56%233</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:48</t>
+          <t>2026-09-09 19:34:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6139亞翔工程</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>+1.08%750</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5550</v>
+        <v>750</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.21%22,000</t>
+          <t>1.21%165,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>22000</v>
+        <v>165000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6139亞翔工程</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.41%742</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>742</v>
+        <v>5760</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.19%165,000</t>
+          <t>1.20%22,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>165000</v>
+        <v>22000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>-0.35%565</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.95%165,000</t>
+          <t>0.92%165,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.86%2155</t>
+          <t>+0.4%126.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2155</v>
+        <v>126.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.79%36,000</t>
+          <t>0.79%637,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>36000</v>
+        <v>637000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.2%126</t>
+          <t>+6.5%2295</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>126</v>
+        <v>2295</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.77%637,000</t>
+          <t>0.77%36,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>637000</v>
+        <v>36000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.49%1370</t>
+          <t>-1.09%1355</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1370</v>
+        <v>1355</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.72%52,872</t>
+          <t>0.71%52,872</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.36%186.5</t>
+          <t>+6.17%198</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>+6.17%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>186.5</v>
+        <v>198</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.2%907</t>
+          <t>+0.99%916</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.62%68,000</t>
+          <t>0.61%68,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.56%189.5</t>
+          <t>+1.06%191.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>189.5</v>
+        <v>191.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.13%2635</t>
+          <t>-3.04%2555</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2635</v>
+        <v>2555</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.55%22,000</t>
+          <t>0.57%22,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.32%3620</t>
+          <t>-0.28%3610</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3620</v>
+        <v>3610</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.54%16,000</t>
+          <t>0.57%16,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.97%520</t>
+          <t>+1.15%526</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.54%108,000</t>
+          <t>0.55%108,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.48%2085</t>
+          <t>0%2085</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.61%275.5</t>
+          <t>+2%281</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+2%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>275.5</v>
+        <v>281</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.83%484</t>
+          <t>+5.17%509</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>+5.17%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:49</t>
+          <t>2026-09-09 19:34:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2347聯強</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.75%231</t>
+          <t>-0.34%88.6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>231</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.39%165,000</t>
+          <t>0.39%448,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>165000</v>
+        <v>448000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:51</t>
+          <t>2026-09-09 19:34:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2347聯強</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.45%88.9</t>
+          <t>-1.3%228</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>88.90000000000001</v>
+        <v>228</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.39%448,000</t>
+          <t>0.38%165,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>448000</v>
+        <v>165000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:51</t>
+          <t>2026-09-09 19:34:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.91%410</t>
+          <t>+1.71%417</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:51</t>
+          <t>2026-09-09 19:34:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.48%104.5</t>
+          <t>+0.48%105</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>104.5</v>
+        <v>105</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:51</t>
+          <t>2026-09-09 19:34:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.65%268.5</t>
+          <t>+0.56%270</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>268.5</v>
+        <v>270</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.36%134,000</t>
+          <t>0.35%134,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:51</t>
+          <t>2026-09-09 19:34:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.55%172</t>
+          <t>+7.27%184.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>+7.27%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>172</v>
+        <v>184.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.34%196,000</t>
+          <t>0.33%196,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:51</t>
+          <t>2026-09-09 19:34:33</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+0.57%70.6</t>
+          <t>-1.27%69.7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">

--- a/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:29</t>
+          <t>2026-09-09 22:37:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:30</t>
+          <t>2026-09-09 22:37:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:31</t>
+          <t>2026-09-09 22:37:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:33</t>
+          <t>2026-09-09 22:37:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:33</t>
+          <t>2026-09-09 22:37:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:33</t>
+          <t>2026-09-09 22:37:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:33</t>
+          <t>2026-09-09 22:37:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:33</t>
+          <t>2026-09-09 22:37:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:33</t>
+          <t>2026-09-09 22:37:59</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:55</t>
+          <t>2026-09-09 22:49:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:56</t>
+          <t>2026-09-09 22:49:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:58</t>
+          <t>2026-09-09 22:49:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:59</t>
+          <t>2026-09-09 22:49:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:59</t>
+          <t>2026-09-09 22:49:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:59</t>
+          <t>2026-09-09 22:49:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:59</t>
+          <t>2026-09-09 22:49:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:59</t>
+          <t>2026-09-09 22:49:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:59</t>
+          <t>2026-09-09 22:49:50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:46</t>
+          <t>2026-09-09 23:10:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:48</t>
+          <t>2026-09-09 23:10:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:49</t>
+          <t>2026-09-09 23:10:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:50</t>
+          <t>2026-09-09 23:10:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:50</t>
+          <t>2026-09-09 23:10:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:50</t>
+          <t>2026-09-09 23:10:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:50</t>
+          <t>2026-09-09 23:10:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:50</t>
+          <t>2026-09-09 23:10:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:50</t>
+          <t>2026-09-09 23:10:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
